--- a/jogos_2025-06-18.xlsx
+++ b/jogos_2025-06-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="125">
   <si>
     <t>Date</t>
   </si>
@@ -229,9 +229,6 @@
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
-    <t>Uzbekistan Uzbekistan Super League</t>
-  </si>
-  <si>
     <t>Norway First Division</t>
   </si>
   <si>
@@ -256,57 +253,54 @@
     <t>Sichuan Jiuniu</t>
   </si>
   <si>
+    <t>Ilves</t>
+  </si>
+  <si>
     <t>Mariehamn</t>
   </si>
   <si>
-    <t>Ilves</t>
+    <t>Tallinna FC Levadia</t>
   </si>
   <si>
     <t>Trans</t>
   </si>
   <si>
-    <t>Tallinna FC Levadia</t>
-  </si>
-  <si>
-    <t>Andijan</t>
-  </si>
-  <si>
     <t>Vaprus</t>
   </si>
   <si>
     <t>Stabæk</t>
   </si>
   <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Moss</t>
+  </si>
+  <si>
     <t>Lyn</t>
   </si>
   <si>
+    <t>Skeid</t>
+  </si>
+  <si>
     <t>Lillestrøm</t>
   </si>
   <si>
-    <t>Skeid</t>
+    <t>Nõmme Kalju</t>
   </si>
   <si>
     <t>Ranheim</t>
   </si>
   <si>
-    <t>Moss</t>
-  </si>
-  <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Nõmme Kalju</t>
-  </si>
-  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
+    <t>Jaro</t>
+  </si>
+  <si>
     <t>HJK</t>
   </si>
   <si>
-    <t>Jaro</t>
-  </si>
-  <si>
     <t>VPS</t>
   </si>
   <si>
@@ -331,55 +325,52 @@
     <t>Wuhan Three Towns</t>
   </si>
   <si>
+    <t>SJK</t>
+  </si>
+  <si>
     <t>KuPS</t>
   </si>
   <si>
-    <t>SJK</t>
+    <t>Tallinna Kalev</t>
   </si>
   <si>
     <t>Tallinna FC Flora</t>
   </si>
   <si>
-    <t>Tallinna Kalev</t>
-  </si>
-  <si>
-    <t>Qizilqum</t>
-  </si>
-  <si>
     <t>Paide</t>
   </si>
   <si>
     <t>Egersund</t>
   </si>
   <si>
+    <t>Mjøndalen</t>
+  </si>
+  <si>
+    <t>Hødd</t>
+  </si>
+  <si>
     <t>Raufoss</t>
   </si>
   <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
     <t>Åsane</t>
   </si>
   <si>
-    <t>Sogndal</t>
+    <t>Harju Jalgpallikool</t>
   </si>
   <si>
     <t>Start</t>
   </si>
   <si>
-    <t>Hødd</t>
-  </si>
-  <si>
-    <t>Mjøndalen</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Aalesund</t>
   </si>
   <si>
+    <t>Oulu</t>
+  </si>
+  <si>
     <t>Haka</t>
-  </si>
-  <si>
-    <t>Oulu</t>
   </si>
   <si>
     <t>Gnistan</t>
@@ -761,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD26"/>
+  <dimension ref="A1:BD25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:56">
@@ -945,13 +936,13 @@
         <v>67</v>
       </c>
       <c r="D2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" t="s">
         <v>75</v>
       </c>
-      <c r="E2" t="s">
-        <v>76</v>
-      </c>
       <c r="F2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -966,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L2">
         <v>2.71</v>
@@ -1041,10 +1032,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL2">
         <v>1.42</v>
@@ -1115,13 +1106,13 @@
         <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1136,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L3">
         <v>3.06</v>
@@ -1211,10 +1202,10 @@
         <v>1.15</v>
       </c>
       <c r="AJ3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL3">
         <v>1.67</v>
@@ -1285,13 +1276,13 @@
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1306,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L4">
         <v>2.7</v>
@@ -1381,10 +1372,10 @@
         <v>1.18</v>
       </c>
       <c r="AJ4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL4">
         <v>1.97</v>
@@ -1455,13 +1446,13 @@
         <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1476,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L5">
         <v>2.51</v>
@@ -1551,10 +1542,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL5">
         <v>1.47</v>
@@ -1625,13 +1616,13 @@
         <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1646,139 +1637,139 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L6">
-        <v>6</v>
+        <v>1.55</v>
       </c>
       <c r="M6">
-        <v>4.48</v>
+        <v>4.2</v>
       </c>
       <c r="N6">
-        <v>1.47</v>
+        <v>4.2</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>1.49</v>
       </c>
       <c r="P6">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="Q6">
-        <v>1.42</v>
+        <v>2.7</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S6">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="T6">
-        <v>2.65</v>
+        <v>2.26</v>
       </c>
       <c r="U6">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="V6">
-        <v>5.75</v>
+        <v>4.5</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z6">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AA6">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AB6">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AC6">
-        <v>2.11</v>
+        <v>2.52</v>
       </c>
       <c r="AD6">
-        <v>2.7</v>
+        <v>2.02</v>
       </c>
       <c r="AE6">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AF6">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AH6">
-        <v>4.75</v>
+        <v>4.12</v>
       </c>
       <c r="AI6">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AJ6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL6">
         <v>1.22</v>
       </c>
       <c r="AM6">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AN6">
-        <v>1.13</v>
+        <v>2.15</v>
       </c>
       <c r="AO6">
         <v>-1</v>
       </c>
       <c r="AP6">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AQ6">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AR6">
+        <v>1.71</v>
+      </c>
+      <c r="AS6">
+        <v>2</v>
+      </c>
+      <c r="AT6">
+        <v>2.65</v>
+      </c>
+      <c r="AU6">
+        <v>3.55</v>
+      </c>
+      <c r="AV6">
+        <v>3</v>
+      </c>
+      <c r="AW6">
+        <v>2.31</v>
+      </c>
+      <c r="AX6">
         <v>1.65</v>
       </c>
-      <c r="AS6">
-        <v>2.05</v>
-      </c>
-      <c r="AT6">
-        <v>2.55</v>
-      </c>
-      <c r="AU6">
-        <v>3.75</v>
-      </c>
-      <c r="AV6">
+      <c r="AY6">
+        <v>1.42</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>1.49</v>
+      </c>
+      <c r="BC6">
         <v>2.7</v>
-      </c>
-      <c r="AW6">
-        <v>2.1</v>
-      </c>
-      <c r="AX6">
-        <v>1.7</v>
-      </c>
-      <c r="AY6">
-        <v>1.44</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>3.2</v>
-      </c>
-      <c r="BC6">
-        <v>1.42</v>
       </c>
       <c r="BD6" s="3">
         <v>45826.45833333334</v>
@@ -1795,13 +1786,13 @@
         <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1816,94 +1807,94 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L7">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="N7">
-        <v>4.64</v>
+        <v>1.4</v>
       </c>
       <c r="O7">
-        <v>1.49</v>
+        <v>3.2</v>
       </c>
       <c r="P7">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="Q7">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="R7">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T7">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="U7">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="V7">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="W7">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>12</v>
       </c>
       <c r="Z7">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AA7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB7">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AC7">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="AD7">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AE7">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AF7">
-        <v>1.47</v>
+        <v>1.83</v>
       </c>
       <c r="AG7">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AH7">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AI7">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL7">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AM7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AN7">
-        <v>2.2</v>
+        <v>1.08</v>
       </c>
       <c r="AO7">
         <v>-1</v>
@@ -1912,31 +1903,31 @@
         <v>1.19</v>
       </c>
       <c r="AQ7">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AR7">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="AS7">
-        <v>1.9</v>
+        <v>2.21</v>
       </c>
       <c r="AT7">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="AU7">
         <v>4.1</v>
       </c>
       <c r="AV7">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="AW7">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AX7">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AY7">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -1945,10 +1936,10 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>1.49</v>
+        <v>3.2</v>
       </c>
       <c r="BC7">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="BD7" s="3">
         <v>45826.45833333334</v>
@@ -1965,13 +1956,13 @@
         <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1986,94 +1977,94 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L8">
-        <v>3.8</v>
+        <v>1.06</v>
       </c>
       <c r="M8">
-        <v>3.65</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N8">
-        <v>1.88</v>
+        <v>19</v>
       </c>
       <c r="O8">
-        <v>2.6</v>
+        <v>1.08</v>
       </c>
       <c r="P8">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="Q8">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="S8">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="T8">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="U8">
-        <v>1.52</v>
+        <v>2.28</v>
       </c>
       <c r="V8">
-        <v>5.2</v>
+        <v>2.65</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.41</v>
       </c>
       <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
+        <v>36</v>
+      </c>
+      <c r="Z8">
         <v>1.04</v>
       </c>
-      <c r="Y8">
-        <v>11.4</v>
-      </c>
-      <c r="Z8">
-        <v>1.17</v>
-      </c>
       <c r="AA8">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AB8">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="AC8">
-        <v>2.1</v>
+        <v>4.73</v>
       </c>
       <c r="AD8">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="AE8">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="AF8">
-        <v>1.65</v>
+        <v>2.28</v>
       </c>
       <c r="AG8">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="AH8">
-        <v>4.8</v>
+        <v>1.92</v>
       </c>
       <c r="AI8">
-        <v>1.17</v>
+        <v>1.78</v>
       </c>
       <c r="AJ8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL8">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="AM8">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="AN8">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -2115,10 +2106,10 @@
         <v>0</v>
       </c>
       <c r="BB8">
-        <v>2.6</v>
+        <v>1.08</v>
       </c>
       <c r="BC8">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BD8" s="3">
         <v>45826.5</v>
@@ -2135,13 +2126,13 @@
         <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2156,94 +2147,94 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L9">
+        <v>4.1</v>
+      </c>
+      <c r="M9">
+        <v>3.78</v>
+      </c>
+      <c r="N9">
+        <v>1.69</v>
+      </c>
+      <c r="O9">
+        <v>2.6</v>
+      </c>
+      <c r="P9">
+        <v>12</v>
+      </c>
+      <c r="Q9">
+        <v>1.55</v>
+      </c>
+      <c r="R9">
+        <v>1.36</v>
+      </c>
+      <c r="S9">
+        <v>2.89</v>
+      </c>
+      <c r="T9">
+        <v>2.69</v>
+      </c>
+      <c r="U9">
+        <v>1.41</v>
+      </c>
+      <c r="V9">
+        <v>6.75</v>
+      </c>
+      <c r="W9">
+        <v>1.04</v>
+      </c>
+      <c r="X9">
         <v>1.02</v>
       </c>
-      <c r="M9">
-        <v>11</v>
-      </c>
-      <c r="N9">
-        <v>30</v>
-      </c>
-      <c r="O9">
-        <v>1.08</v>
-      </c>
-      <c r="P9">
-        <v>36</v>
-      </c>
-      <c r="Q9">
-        <v>8</v>
-      </c>
-      <c r="R9">
-        <v>1.08</v>
-      </c>
-      <c r="S9">
-        <v>6.5</v>
-      </c>
-      <c r="T9">
-        <v>1.5</v>
-      </c>
-      <c r="U9">
-        <v>2.4</v>
-      </c>
-      <c r="V9">
-        <v>2.55</v>
-      </c>
-      <c r="W9">
-        <v>1.45</v>
-      </c>
-      <c r="X9">
-        <v>1.01</v>
-      </c>
       <c r="Y9">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AA9">
-        <v>13</v>
+        <v>3.55</v>
       </c>
       <c r="AB9">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>2.11</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AE9">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF9">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AG9">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AH9">
-        <v>1.91</v>
+        <v>5.5</v>
       </c>
       <c r="AI9">
-        <v>1.86</v>
+        <v>1.07</v>
       </c>
       <c r="AJ9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL9">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AM9">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AN9">
-        <v>8</v>
+        <v>1.27</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -2285,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>1.08</v>
+        <v>2.6</v>
       </c>
       <c r="BC9">
-        <v>8</v>
+        <v>1.55</v>
       </c>
       <c r="BD9" s="3">
         <v>45826.5</v>
@@ -2302,16 +2293,16 @@
         <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2326,94 +2317,94 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L10">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="M10">
-        <v>3.3</v>
+        <v>3.99</v>
       </c>
       <c r="N10">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK10" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO10">
         <v>-1</v>
@@ -2455,10 +2446,10 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BD10" s="3">
         <v>45826.54166666666</v>
@@ -2469,19 +2460,19 @@
         <v>45826</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2496,127 +2487,127 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L11">
-        <v>5</v>
+        <v>1.76</v>
       </c>
       <c r="M11">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="N11">
-        <v>1.6</v>
+        <v>3.79</v>
       </c>
       <c r="O11">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="P11">
-        <v>13</v>
+        <v>18.25</v>
       </c>
       <c r="Q11">
-        <v>1.46</v>
+        <v>2.29</v>
       </c>
       <c r="R11">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S11">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="T11">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="U11">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="V11">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Z11">
         <v>1.17</v>
       </c>
       <c r="AA11">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AB11">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="AC11">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AD11">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="AE11">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AF11">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AH11">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="AI11">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AJ11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL11">
         <v>1.25</v>
       </c>
       <c r="AM11">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AN11">
-        <v>1.18</v>
+        <v>2.05</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2625,13 +2616,13 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="BC11">
-        <v>1.46</v>
+        <v>2.29</v>
       </c>
       <c r="BD11" s="3">
-        <v>45826.54166666666</v>
+        <v>45826.58333333334</v>
       </c>
     </row>
     <row r="12" spans="1:56">
@@ -2642,16 +2633,16 @@
         <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2666,43 +2657,43 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L12">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="M12">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N12">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="O12">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="P12">
-        <v>18.25</v>
+        <v>16.25</v>
       </c>
       <c r="Q12">
-        <v>2.29</v>
+        <v>4</v>
       </c>
       <c r="R12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T12">
         <v>2.25</v>
       </c>
       <c r="U12">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V12">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="W12">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2711,83 +2702,83 @@
         <v>15</v>
       </c>
       <c r="Z12">
+        <v>1.18</v>
+      </c>
+      <c r="AA12">
+        <v>4.9</v>
+      </c>
+      <c r="AB12">
+        <v>1.57</v>
+      </c>
+      <c r="AC12">
+        <v>2.15</v>
+      </c>
+      <c r="AD12">
+        <v>2.25</v>
+      </c>
+      <c r="AE12">
+        <v>1.56</v>
+      </c>
+      <c r="AF12">
+        <v>1.7</v>
+      </c>
+      <c r="AG12">
+        <v>1.95</v>
+      </c>
+      <c r="AH12">
+        <v>3.92</v>
+      </c>
+      <c r="AI12">
+        <v>1.18</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>124</v>
+      </c>
+      <c r="AL12">
         <v>1.15</v>
       </c>
-      <c r="AA12">
-        <v>4.8</v>
-      </c>
-      <c r="AB12">
-        <v>1.53</v>
-      </c>
-      <c r="AC12">
-        <v>2.45</v>
-      </c>
-      <c r="AD12">
-        <v>2.3</v>
-      </c>
-      <c r="AE12">
-        <v>1.53</v>
-      </c>
-      <c r="AF12">
-        <v>1.49</v>
-      </c>
-      <c r="AG12">
-        <v>2.38</v>
-      </c>
-      <c r="AH12">
-        <v>3.9</v>
-      </c>
-      <c r="AI12">
-        <v>1.2</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>127</v>
-      </c>
-      <c r="AK12" t="s">
-        <v>127</v>
-      </c>
-      <c r="AL12">
-        <v>1.25</v>
-      </c>
       <c r="AM12">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AN12">
-        <v>1.95</v>
+        <v>2.65</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AQ12">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AR12">
+        <v>1.55</v>
+      </c>
+      <c r="AS12">
+        <v>1.75</v>
+      </c>
+      <c r="AT12">
+        <v>2.19</v>
+      </c>
+      <c r="AU12">
+        <v>4.1</v>
+      </c>
+      <c r="AV12">
+        <v>2.9</v>
+      </c>
+      <c r="AW12">
+        <v>2.23</v>
+      </c>
+      <c r="AX12">
+        <v>2.01</v>
+      </c>
+      <c r="AY12">
         <v>1.63</v>
       </c>
-      <c r="AS12">
-        <v>1.82</v>
-      </c>
-      <c r="AT12">
-        <v>2.27</v>
-      </c>
-      <c r="AU12">
-        <v>4.5</v>
-      </c>
-      <c r="AV12">
-        <v>3.2</v>
-      </c>
-      <c r="AW12">
-        <v>2.39</v>
-      </c>
-      <c r="AX12">
-        <v>1.92</v>
-      </c>
-      <c r="AY12">
-        <v>1.59</v>
-      </c>
       <c r="AZ12">
         <v>0</v>
       </c>
@@ -2795,10 +2786,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.63</v>
+        <v>1.29</v>
       </c>
       <c r="BC12">
-        <v>2.29</v>
+        <v>4</v>
       </c>
       <c r="BD12" s="3">
         <v>45826.58333333334</v>
@@ -2812,16 +2803,16 @@
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2836,43 +2827,43 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L13">
+        <v>2.01</v>
+      </c>
+      <c r="M13">
+        <v>3.4</v>
+      </c>
+      <c r="N13">
+        <v>3.25</v>
+      </c>
+      <c r="O13">
+        <v>1.73</v>
+      </c>
+      <c r="P13">
+        <v>14.75</v>
+      </c>
+      <c r="Q13">
         <v>2.2</v>
       </c>
-      <c r="M13">
-        <v>3.6</v>
-      </c>
-      <c r="N13">
-        <v>3.03</v>
-      </c>
-      <c r="O13">
-        <v>2.2</v>
-      </c>
-      <c r="P13">
-        <v>9</v>
-      </c>
-      <c r="Q13">
-        <v>1.8</v>
-      </c>
       <c r="R13">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S13">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="T13">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="U13">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V13">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
         <v>1.04</v>
@@ -2881,82 +2872,82 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA13">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AB13">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AC13">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AD13">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AE13">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF13">
         <v>1.62</v>
       </c>
       <c r="AG13">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH13">
-        <v>4.7</v>
+        <v>5.25</v>
       </c>
       <c r="AI13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AJ13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK13" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL13">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AM13">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN13">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AR13">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AS13">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AT13">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="AU13">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="AV13">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="AW13">
-        <v>2.52</v>
+        <v>2.17</v>
       </c>
       <c r="AX13">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="AY13">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -2965,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
+        <v>1.73</v>
+      </c>
+      <c r="BC13">
         <v>2.2</v>
-      </c>
-      <c r="BC13">
-        <v>1.8</v>
       </c>
       <c r="BD13" s="3">
         <v>45826.58333333334</v>
@@ -2982,16 +2973,16 @@
         <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -3006,127 +2997,127 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L14">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="M14">
-        <v>6.1</v>
+        <v>3.52</v>
       </c>
       <c r="N14">
+        <v>2.86</v>
+      </c>
+      <c r="O14">
+        <v>2.2</v>
+      </c>
+      <c r="P14">
+        <v>9</v>
+      </c>
+      <c r="Q14">
+        <v>1.8</v>
+      </c>
+      <c r="R14">
+        <v>1.33</v>
+      </c>
+      <c r="S14">
+        <v>2.95</v>
+      </c>
+      <c r="T14">
+        <v>2.45</v>
+      </c>
+      <c r="U14">
+        <v>1.44</v>
+      </c>
+      <c r="V14">
+        <v>5.5</v>
+      </c>
+      <c r="W14">
+        <v>1.11</v>
+      </c>
+      <c r="X14">
+        <v>1.04</v>
+      </c>
+      <c r="Y14">
         <v>10.5</v>
       </c>
-      <c r="O14">
-        <v>1.17</v>
-      </c>
-      <c r="P14">
-        <v>20.5</v>
-      </c>
-      <c r="Q14">
-        <v>5.5</v>
-      </c>
-      <c r="R14">
-        <v>1.22</v>
-      </c>
-      <c r="S14">
+      <c r="Z14">
+        <v>1.25</v>
+      </c>
+      <c r="AA14">
         <v>3.7</v>
       </c>
-      <c r="T14">
-        <v>1.97</v>
-      </c>
-      <c r="U14">
+      <c r="AB14">
+        <v>1.76</v>
+      </c>
+      <c r="AC14">
+        <v>1.94</v>
+      </c>
+      <c r="AD14">
+        <v>3</v>
+      </c>
+      <c r="AE14">
+        <v>1.36</v>
+      </c>
+      <c r="AF14">
         <v>1.67</v>
       </c>
-      <c r="V14">
-        <v>3.9</v>
-      </c>
-      <c r="W14">
-        <v>1.2</v>
-      </c>
-      <c r="X14">
-        <v>1.02</v>
-      </c>
-      <c r="Y14">
-        <v>19</v>
-      </c>
-      <c r="Z14">
-        <v>1.12</v>
-      </c>
-      <c r="AA14">
-        <v>5.5</v>
-      </c>
-      <c r="AB14">
-        <v>1.44</v>
-      </c>
-      <c r="AC14">
-        <v>2.63</v>
-      </c>
-      <c r="AD14">
+      <c r="AG14">
         <v>2.15</v>
       </c>
-      <c r="AE14">
-        <v>1.65</v>
-      </c>
-      <c r="AF14">
-        <v>1.85</v>
-      </c>
-      <c r="AG14">
-        <v>1.91</v>
-      </c>
       <c r="AH14">
-        <v>3.6</v>
+        <v>5.91</v>
       </c>
       <c r="AI14">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AJ14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK14" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL14">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AM14">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AN14">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AQ14">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AR14">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="AS14">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AT14">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AU14">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="AV14">
-        <v>3.58</v>
+        <v>2.95</v>
       </c>
       <c r="AW14">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AX14">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AY14">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3135,10 +3126,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.17</v>
+        <v>2.2</v>
       </c>
       <c r="BC14">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="BD14" s="3">
         <v>45826.58333333334</v>
@@ -3152,16 +3143,16 @@
         <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -3176,16 +3167,16 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L15">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="M15">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="N15">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="O15">
         <v>2.5</v>
@@ -3197,73 +3188,73 @@
         <v>1.53</v>
       </c>
       <c r="R15">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S15">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="T15">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="U15">
         <v>1.5</v>
       </c>
       <c r="V15">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>11</v>
       </c>
       <c r="Z15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AA15">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB15">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD15">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AE15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH15">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="AI15">
         <v>1.17</v>
       </c>
       <c r="AJ15" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK15" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL15">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AM15">
         <v>1.25</v>
       </c>
       <c r="AN15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AO15">
         <v>-1</v>
@@ -3272,31 +3263,31 @@
         <v>1.18</v>
       </c>
       <c r="AQ15">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AR15">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AS15">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AT15">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AU15">
         <v>4.1</v>
       </c>
       <c r="AV15">
-        <v>2.98</v>
+        <v>2.55</v>
       </c>
       <c r="AW15">
         <v>2.27</v>
       </c>
       <c r="AX15">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AY15">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3322,16 +3313,16 @@
         <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -3346,127 +3337,127 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L16">
-        <v>2.32</v>
+        <v>1.23</v>
       </c>
       <c r="M16">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="N16">
-        <v>2.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O16">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="Q16">
+        <v>5.5</v>
+      </c>
+      <c r="R16">
+        <v>1.22</v>
+      </c>
+      <c r="S16">
+        <v>3.9</v>
+      </c>
+      <c r="T16">
+        <v>2.05</v>
+      </c>
+      <c r="U16">
+        <v>1.7</v>
+      </c>
+      <c r="V16">
+        <v>4.5</v>
+      </c>
+      <c r="W16">
+        <v>1.17</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>16</v>
+      </c>
+      <c r="Z16">
+        <v>1.14</v>
+      </c>
+      <c r="AA16">
+        <v>5</v>
+      </c>
+      <c r="AB16">
+        <v>1.43</v>
+      </c>
+      <c r="AC16">
+        <v>2.62</v>
+      </c>
+      <c r="AD16">
         <v>2.1</v>
       </c>
-      <c r="R16">
-        <v>1.3</v>
-      </c>
-      <c r="S16">
-        <v>3.1</v>
-      </c>
-      <c r="T16">
-        <v>2.3</v>
-      </c>
-      <c r="U16">
-        <v>1.55</v>
-      </c>
-      <c r="V16">
-        <v>5.1</v>
-      </c>
-      <c r="W16">
-        <v>1.11</v>
-      </c>
-      <c r="X16">
-        <v>1</v>
-      </c>
-      <c r="Y16">
-        <v>15</v>
-      </c>
-      <c r="Z16">
-        <v>1.18</v>
-      </c>
-      <c r="AA16">
-        <v>4.33</v>
-      </c>
-      <c r="AB16">
-        <v>1.55</v>
-      </c>
-      <c r="AC16">
-        <v>2.25</v>
-      </c>
-      <c r="AD16">
-        <v>2.48</v>
-      </c>
       <c r="AE16">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AF16">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="AG16">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AH16">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AI16">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AJ16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK16" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL16">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AM16">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AN16">
-        <v>1.45</v>
+        <v>3.3</v>
       </c>
       <c r="AO16">
         <v>-1</v>
       </c>
       <c r="AP16">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AQ16">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AR16">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AS16">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AT16">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="AU16">
-        <v>4.45</v>
+        <v>4.9</v>
       </c>
       <c r="AV16">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="AW16">
-        <v>2.39</v>
+        <v>2.67</v>
       </c>
       <c r="AX16">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="AY16">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -3475,10 +3466,10 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="BC16">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="BD16" s="3">
         <v>45826.58333333334</v>
@@ -3492,16 +3483,16 @@
         <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3516,139 +3507,139 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L17">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="M17">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="N17">
-        <v>3.37</v>
+        <v>6.2</v>
       </c>
       <c r="O17">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="P17">
-        <v>14.75</v>
+        <v>12.5</v>
       </c>
       <c r="Q17">
+        <v>3.4</v>
+      </c>
+      <c r="R17">
+        <v>1.2</v>
+      </c>
+      <c r="S17">
+        <v>3.8</v>
+      </c>
+      <c r="T17">
+        <v>2</v>
+      </c>
+      <c r="U17">
+        <v>1.76</v>
+      </c>
+      <c r="V17">
+        <v>3.8</v>
+      </c>
+      <c r="W17">
+        <v>1.2</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>21</v>
+      </c>
+      <c r="Z17">
+        <v>1.1</v>
+      </c>
+      <c r="AA17">
+        <v>5.75</v>
+      </c>
+      <c r="AB17">
+        <v>1.44</v>
+      </c>
+      <c r="AC17">
+        <v>2.59</v>
+      </c>
+      <c r="AD17">
+        <v>2.21</v>
+      </c>
+      <c r="AE17">
+        <v>1.59</v>
+      </c>
+      <c r="AF17">
+        <v>1.62</v>
+      </c>
+      <c r="AG17">
         <v>2.2</v>
       </c>
-      <c r="R17">
+      <c r="AH17">
+        <v>3.1</v>
+      </c>
+      <c r="AI17">
         <v>1.3</v>
       </c>
-      <c r="S17">
-        <v>3.1</v>
-      </c>
-      <c r="T17">
-        <v>2.55</v>
-      </c>
-      <c r="U17">
-        <v>1.45</v>
-      </c>
-      <c r="V17">
-        <v>6.7</v>
-      </c>
-      <c r="W17">
-        <v>1.09</v>
-      </c>
-      <c r="X17">
-        <v>1.02</v>
-      </c>
-      <c r="Y17">
-        <v>10</v>
-      </c>
-      <c r="Z17">
-        <v>1.22</v>
-      </c>
-      <c r="AA17">
-        <v>3.6</v>
-      </c>
-      <c r="AB17">
-        <v>1.8</v>
-      </c>
-      <c r="AC17">
-        <v>1.91</v>
-      </c>
-      <c r="AD17">
+      <c r="AJ17" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>124</v>
+      </c>
+      <c r="AL17">
+        <v>1.18</v>
+      </c>
+      <c r="AM17">
+        <v>1.21</v>
+      </c>
+      <c r="AN17">
         <v>3</v>
-      </c>
-      <c r="AE17">
-        <v>1.33</v>
-      </c>
-      <c r="AF17">
-        <v>1.67</v>
-      </c>
-      <c r="AG17">
-        <v>2.1</v>
-      </c>
-      <c r="AH17">
-        <v>5.5</v>
-      </c>
-      <c r="AI17">
-        <v>1.13</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>127</v>
-      </c>
-      <c r="AK17" t="s">
-        <v>127</v>
-      </c>
-      <c r="AL17">
-        <v>1.3</v>
-      </c>
-      <c r="AM17">
-        <v>1.28</v>
-      </c>
-      <c r="AN17">
-        <v>1.7</v>
       </c>
       <c r="AO17">
         <v>-1</v>
       </c>
       <c r="AP17">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
         <v>1.36</v>
       </c>
-      <c r="AR17">
-        <v>1.81</v>
-      </c>
-      <c r="AS17">
-        <v>2.03</v>
-      </c>
-      <c r="AT17">
-        <v>2.53</v>
-      </c>
-      <c r="AU17">
-        <v>3.88</v>
-      </c>
-      <c r="AV17">
-        <v>2.77</v>
-      </c>
-      <c r="AW17">
-        <v>2.16</v>
-      </c>
-      <c r="AX17">
-        <v>1.74</v>
-      </c>
-      <c r="AY17">
-        <v>1.46</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.73</v>
-      </c>
       <c r="BC17">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="BD17" s="3">
         <v>45826.58333333334</v>
@@ -3662,16 +3653,16 @@
         <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -3686,128 +3677,128 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L18">
-        <v>1.51</v>
+        <v>2.12</v>
       </c>
       <c r="M18">
-        <v>4.35</v>
+        <v>3.58</v>
       </c>
       <c r="N18">
-        <v>5.5</v>
+        <v>2.87</v>
       </c>
       <c r="O18">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="P18">
-        <v>16.25</v>
+        <v>17</v>
       </c>
       <c r="Q18">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="R18">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S18">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T18">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U18">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="V18">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z18">
         <v>1.18</v>
       </c>
       <c r="AA18">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AB18">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC18">
         <v>2.2</v>
       </c>
       <c r="AD18">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AE18">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF18">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AG18">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AH18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AI18">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AJ18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL18">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AM18">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="AN18">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="AO18">
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AQ18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AR18">
+        <v>1.65</v>
+      </c>
+      <c r="AS18">
+        <v>1.87</v>
+      </c>
+      <c r="AT18">
+        <v>2.32</v>
+      </c>
+      <c r="AU18">
+        <v>4.4</v>
+      </c>
+      <c r="AV18">
+        <v>3.2</v>
+      </c>
+      <c r="AW18">
+        <v>2.39</v>
+      </c>
+      <c r="AX18">
+        <v>1.9</v>
+      </c>
+      <c r="AY18">
         <v>1.55</v>
       </c>
-      <c r="AS18">
-        <v>1.75</v>
-      </c>
-      <c r="AT18">
-        <v>2.17</v>
-      </c>
-      <c r="AU18">
-        <v>4.8</v>
-      </c>
-      <c r="AV18">
-        <v>3.38</v>
-      </c>
-      <c r="AW18">
-        <v>2.23</v>
-      </c>
-      <c r="AX18">
-        <v>2</v>
-      </c>
-      <c r="AY18">
-        <v>1.65</v>
-      </c>
       <c r="AZ18">
         <v>0</v>
       </c>
@@ -3815,10 +3806,10 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="BC18">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="BD18" s="3">
         <v>45826.58333333334</v>
@@ -3832,16 +3823,16 @@
         <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -3856,127 +3847,127 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L19">
-        <v>1.33</v>
+        <v>2.04</v>
       </c>
       <c r="M19">
-        <v>5.1</v>
+        <v>3.59</v>
       </c>
       <c r="N19">
-        <v>7.48</v>
+        <v>3.01</v>
       </c>
       <c r="O19">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="P19">
-        <v>12.5</v>
+        <v>15.75</v>
       </c>
       <c r="Q19">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
+        <v>1.3</v>
+      </c>
+      <c r="S19">
+        <v>3.2</v>
+      </c>
+      <c r="T19">
+        <v>2.35</v>
+      </c>
+      <c r="U19">
+        <v>1.51</v>
+      </c>
+      <c r="V19">
+        <v>5.5</v>
+      </c>
+      <c r="W19">
+        <v>1.12</v>
+      </c>
+      <c r="X19">
+        <v>1.04</v>
+      </c>
+      <c r="Y19">
+        <v>13</v>
+      </c>
+      <c r="Z19">
         <v>1.2</v>
       </c>
-      <c r="S19">
-        <v>3.8</v>
-      </c>
-      <c r="T19">
-        <v>2.17</v>
-      </c>
-      <c r="U19">
-        <v>1.67</v>
-      </c>
-      <c r="V19">
-        <v>4.3</v>
-      </c>
-      <c r="W19">
-        <v>1.17</v>
-      </c>
-      <c r="X19">
-        <v>1.03</v>
-      </c>
-      <c r="Y19">
-        <v>19</v>
-      </c>
-      <c r="Z19">
-        <v>1.14</v>
-      </c>
       <c r="AA19">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AB19">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AC19">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AD19">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="AE19">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH19">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="AI19">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AJ19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK19" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL19">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AM19">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AN19">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AO19">
         <v>-1</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AZ19">
         <v>0</v>
@@ -3985,10 +3976,10 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="BC19">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="BD19" s="3">
         <v>45826.58333333334</v>
@@ -3999,19 +3990,19 @@
         <v>45826</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -4026,127 +4017,127 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L20">
+        <v>2.51</v>
+      </c>
+      <c r="M20">
+        <v>3.27</v>
+      </c>
+      <c r="N20">
+        <v>2.4</v>
+      </c>
+      <c r="O20">
+        <v>2</v>
+      </c>
+      <c r="P20">
+        <v>7.75</v>
+      </c>
+      <c r="Q20">
+        <v>2</v>
+      </c>
+      <c r="R20">
+        <v>1.42</v>
+      </c>
+      <c r="S20">
+        <v>2.62</v>
+      </c>
+      <c r="T20">
+        <v>2.93</v>
+      </c>
+      <c r="U20">
+        <v>1.36</v>
+      </c>
+      <c r="V20">
+        <v>7.5</v>
+      </c>
+      <c r="W20">
+        <v>1.07</v>
+      </c>
+      <c r="X20">
+        <v>1.06</v>
+      </c>
+      <c r="Y20">
+        <v>8.5</v>
+      </c>
+      <c r="Z20">
+        <v>1.36</v>
+      </c>
+      <c r="AA20">
+        <v>3</v>
+      </c>
+      <c r="AB20">
+        <v>1.91</v>
+      </c>
+      <c r="AC20">
+        <v>1.79</v>
+      </c>
+      <c r="AD20">
+        <v>3.55</v>
+      </c>
+      <c r="AE20">
+        <v>1.25</v>
+      </c>
+      <c r="AF20">
+        <v>1.77</v>
+      </c>
+      <c r="AG20">
         <v>1.95</v>
       </c>
-      <c r="M20">
-        <v>3.55</v>
-      </c>
-      <c r="N20">
-        <v>2.99</v>
-      </c>
-      <c r="O20">
-        <v>1.8</v>
-      </c>
-      <c r="P20">
-        <v>15.75</v>
-      </c>
-      <c r="Q20">
-        <v>2.1</v>
-      </c>
-      <c r="R20">
+      <c r="AH20">
+        <v>6.75</v>
+      </c>
+      <c r="AI20">
+        <v>1.08</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>124</v>
+      </c>
+      <c r="AL20">
         <v>1.3</v>
       </c>
-      <c r="S20">
-        <v>3.1</v>
-      </c>
-      <c r="T20">
-        <v>2.3</v>
-      </c>
-      <c r="U20">
-        <v>1.53</v>
-      </c>
-      <c r="V20">
-        <v>5.25</v>
-      </c>
-      <c r="W20">
-        <v>1.12</v>
-      </c>
-      <c r="X20">
-        <v>1.04</v>
-      </c>
-      <c r="Y20">
-        <v>13</v>
-      </c>
-      <c r="Z20">
-        <v>1.18</v>
-      </c>
-      <c r="AA20">
-        <v>4.33</v>
-      </c>
-      <c r="AB20">
-        <v>1.67</v>
-      </c>
-      <c r="AC20">
-        <v>2.15</v>
-      </c>
-      <c r="AD20">
-        <v>2.4</v>
-      </c>
-      <c r="AE20">
-        <v>1.44</v>
-      </c>
-      <c r="AF20">
-        <v>1.55</v>
-      </c>
-      <c r="AG20">
-        <v>2.3</v>
-      </c>
-      <c r="AH20">
-        <v>4.33</v>
-      </c>
-      <c r="AI20">
-        <v>1.17</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>127</v>
-      </c>
-      <c r="AK20" t="s">
-        <v>127</v>
-      </c>
-      <c r="AL20">
-        <v>1.29</v>
-      </c>
       <c r="AM20">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AN20">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="AO20">
         <v>-1</v>
       </c>
       <c r="AP20">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="AQ20">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AR20">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AS20">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="AT20">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="AU20">
-        <v>4.95</v>
+        <v>3.12</v>
       </c>
       <c r="AV20">
-        <v>3.48</v>
+        <v>2.3</v>
       </c>
       <c r="AW20">
-        <v>2.57</v>
+        <v>1.8</v>
       </c>
       <c r="AX20">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="AY20">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AZ20">
         <v>0</v>
@@ -4155,13 +4146,13 @@
         <v>0</v>
       </c>
       <c r="BB20">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BC20">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="BD20" s="3">
-        <v>45826.58333333334</v>
+        <v>45826.625</v>
       </c>
     </row>
     <row r="21" spans="1:56">
@@ -4175,13 +4166,13 @@
         <v>69</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -4196,16 +4187,16 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L21">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M21">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="N21">
-        <v>6.35</v>
+        <v>4.75</v>
       </c>
       <c r="O21">
         <v>1.38</v>
@@ -4223,61 +4214,61 @@
         <v>3.6</v>
       </c>
       <c r="T21">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="U21">
         <v>1.65</v>
       </c>
       <c r="V21">
-        <v>4.4</v>
+        <v>5.05</v>
       </c>
       <c r="W21">
         <v>1.16</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z21">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AA21">
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AC21">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="AD21">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AE21">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AF21">
         <v>1.67</v>
       </c>
       <c r="AG21">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AH21">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AI21">
         <v>1.22</v>
       </c>
       <c r="AJ21" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK21" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL21">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AM21">
         <v>1.17</v>
@@ -4289,13 +4280,13 @@
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AQ21">
         <v>1.28</v>
       </c>
       <c r="AR21">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AS21">
         <v>1.87</v>
@@ -4345,13 +4336,13 @@
         <v>69</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -4366,127 +4357,127 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L22">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="M22">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="O22">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="P22">
-        <v>7.75</v>
+        <v>11</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="R22">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S22">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="U22">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="V22">
-        <v>7.5</v>
+        <v>5.3</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X22">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="Z22">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AA22">
-        <v>3</v>
+        <v>4.29</v>
       </c>
       <c r="AB22">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="AC22">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="AD22">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="AE22">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF22">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH22">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI22">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AJ22" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK22" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL22">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AM22">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AN22">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AQ22">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AR22">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AS22">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="AT22">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="AU22">
-        <v>3.22</v>
+        <v>3.72</v>
       </c>
       <c r="AV22">
-        <v>2.32</v>
+        <v>2.68</v>
       </c>
       <c r="AW22">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AX22">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AY22">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4495,10 +4486,10 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="BC22">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" s="3">
         <v>45826.625</v>
@@ -4509,19 +4500,19 @@
         <v>45826</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C23" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4536,127 +4527,127 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="L23">
-        <v>1.78</v>
+        <v>4.2</v>
       </c>
       <c r="M23">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N23">
-        <v>3.26</v>
+        <v>1.64</v>
       </c>
       <c r="O23">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="P23">
-        <v>11</v>
+        <v>14.75</v>
       </c>
       <c r="Q23">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="R23">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S23">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="T23">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="U23">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="V23">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="W23">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
         <v>12</v>
       </c>
       <c r="Z23">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AA23">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AB23">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AC23">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AD23">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AE23">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AF23">
         <v>1.6</v>
       </c>
       <c r="AG23">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH23">
-        <v>4.7</v>
+        <v>4.15</v>
       </c>
       <c r="AI23">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AJ23" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK23" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL23">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AM23">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AN23">
-        <v>1.7</v>
+        <v>1.16</v>
       </c>
       <c r="AO23">
         <v>-1</v>
       </c>
       <c r="AP23">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ23">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR23">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS23">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AT23">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AU23">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AV23">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AW23">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AX23">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AY23">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ23">
         <v>0</v>
@@ -4665,13 +4656,13 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="BC23">
-        <v>2.25</v>
+        <v>1.4</v>
       </c>
       <c r="BD23" s="3">
-        <v>45826.625</v>
+        <v>45826.83333333334</v>
       </c>
     </row>
     <row r="24" spans="1:56">
@@ -4679,121 +4670,121 @@
         <v>45826</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F24" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" t="s">
         <v>123</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24" t="s">
-        <v>126</v>
-      </c>
       <c r="L24">
-        <v>5</v>
+        <v>2.63</v>
       </c>
       <c r="M24">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N24">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="O24">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="P24">
-        <v>14.75</v>
+        <v>0</v>
       </c>
       <c r="Q24">
+        <v>2.1</v>
+      </c>
+      <c r="R24">
+        <v>1.35</v>
+      </c>
+      <c r="S24">
+        <v>2.8</v>
+      </c>
+      <c r="T24">
+        <v>2.6</v>
+      </c>
+      <c r="U24">
         <v>1.4</v>
       </c>
-      <c r="R24">
-        <v>1.27</v>
-      </c>
-      <c r="S24">
+      <c r="V24">
+        <v>6.4</v>
+      </c>
+      <c r="W24">
+        <v>1.08</v>
+      </c>
+      <c r="X24">
+        <v>1.04</v>
+      </c>
+      <c r="Y24">
+        <v>8.5</v>
+      </c>
+      <c r="Z24">
+        <v>1.29</v>
+      </c>
+      <c r="AA24">
         <v>3.3</v>
       </c>
-      <c r="T24">
-        <v>2.35</v>
-      </c>
-      <c r="U24">
-        <v>1.5</v>
-      </c>
-      <c r="V24">
-        <v>5.3</v>
-      </c>
-      <c r="W24">
-        <v>1.11</v>
-      </c>
-      <c r="X24">
-        <v>1.01</v>
-      </c>
-      <c r="Y24">
-        <v>11.5</v>
-      </c>
-      <c r="Z24">
-        <v>1.2</v>
-      </c>
-      <c r="AA24">
-        <v>4.3</v>
-      </c>
       <c r="AB24">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC24">
+        <v>1.79</v>
+      </c>
+      <c r="AD24">
+        <v>3.3</v>
+      </c>
+      <c r="AE24">
+        <v>1.33</v>
+      </c>
+      <c r="AF24">
+        <v>1.62</v>
+      </c>
+      <c r="AG24">
         <v>2.1</v>
       </c>
-      <c r="AD24">
-        <v>2.62</v>
-      </c>
-      <c r="AE24">
-        <v>1.47</v>
-      </c>
-      <c r="AF24">
-        <v>1.65</v>
-      </c>
-      <c r="AG24">
-        <v>2.05</v>
-      </c>
       <c r="AH24">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AI24">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AJ24" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AK24" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL24">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AM24">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN24">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AO24">
         <v>-1</v>
@@ -4835,13 +4826,13 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="BC24">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="BD24" s="3">
-        <v>45826.83333333334</v>
+        <v>45826.875</v>
       </c>
     </row>
     <row r="25" spans="1:56">
@@ -4849,121 +4840,121 @@
         <v>45826</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
         <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" t="s">
+        <v>123</v>
+      </c>
+      <c r="L25">
+        <v>2.1</v>
+      </c>
+      <c r="M25">
+        <v>3.5</v>
+      </c>
+      <c r="N25">
+        <v>2.9</v>
+      </c>
+      <c r="O25">
+        <v>1.73</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>2.25</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>1.53</v>
+      </c>
+      <c r="AC25">
+        <v>2.37</v>
+      </c>
+      <c r="AD25">
+        <v>2.25</v>
+      </c>
+      <c r="AE25">
+        <v>1.57</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AI25">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="s">
         <v>124</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25" t="s">
-        <v>126</v>
-      </c>
-      <c r="L25">
-        <v>2.46</v>
-      </c>
-      <c r="M25">
-        <v>3.55</v>
-      </c>
-      <c r="N25">
-        <v>2.4</v>
-      </c>
-      <c r="O25">
-        <v>1.8</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>2.1</v>
-      </c>
-      <c r="R25">
-        <v>1.27</v>
-      </c>
-      <c r="S25">
-        <v>3.3</v>
-      </c>
-      <c r="T25">
-        <v>2.36</v>
-      </c>
-      <c r="U25">
-        <v>1.52</v>
-      </c>
-      <c r="V25">
-        <v>5.2</v>
-      </c>
-      <c r="W25">
-        <v>1.12</v>
-      </c>
-      <c r="X25">
-        <v>1.03</v>
-      </c>
-      <c r="Y25">
-        <v>11.9</v>
-      </c>
-      <c r="Z25">
-        <v>1.17</v>
-      </c>
-      <c r="AA25">
-        <v>4.4</v>
-      </c>
-      <c r="AB25">
-        <v>1.66</v>
-      </c>
-      <c r="AC25">
-        <v>2.15</v>
-      </c>
-      <c r="AD25">
-        <v>2.5</v>
-      </c>
-      <c r="AE25">
-        <v>1.52</v>
-      </c>
-      <c r="AF25">
-        <v>1.45</v>
-      </c>
-      <c r="AG25">
-        <v>2.45</v>
-      </c>
-      <c r="AH25">
-        <v>4.3</v>
-      </c>
-      <c r="AI25">
-        <v>1.17</v>
-      </c>
-      <c r="AJ25" t="s">
-        <v>127</v>
-      </c>
       <c r="AK25" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="AL25">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AM25">
         <v>0</v>
       </c>
       <c r="AN25">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <v>-1</v>
@@ -5005,182 +4996,12 @@
         <v>0</v>
       </c>
       <c r="BB25">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BC25">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD25" s="3">
-        <v>45826.875</v>
-      </c>
-    </row>
-    <row r="26" spans="1:56">
-      <c r="A26" s="2">
-        <v>45826</v>
-      </c>
-      <c r="B26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" t="s">
-        <v>100</v>
-      </c>
-      <c r="F26" t="s">
-        <v>125</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26" t="s">
-        <v>126</v>
-      </c>
-      <c r="L26">
-        <v>2.1</v>
-      </c>
-      <c r="M26">
-        <v>3.5</v>
-      </c>
-      <c r="N26">
-        <v>2.9</v>
-      </c>
-      <c r="O26">
-        <v>1.73</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>2.25</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="W26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-      <c r="Z26">
-        <v>0</v>
-      </c>
-      <c r="AA26">
-        <v>0</v>
-      </c>
-      <c r="AB26">
-        <v>1.57</v>
-      </c>
-      <c r="AC26">
-        <v>2.35</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AH26">
-        <v>0</v>
-      </c>
-      <c r="AI26">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="s">
-        <v>127</v>
-      </c>
-      <c r="AK26" t="s">
-        <v>127</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>0</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>0</v>
-      </c>
-      <c r="AQ26">
-        <v>0</v>
-      </c>
-      <c r="AR26">
-        <v>0</v>
-      </c>
-      <c r="AS26">
-        <v>0</v>
-      </c>
-      <c r="AT26">
-        <v>0</v>
-      </c>
-      <c r="AU26">
-        <v>0</v>
-      </c>
-      <c r="AV26">
-        <v>0</v>
-      </c>
-      <c r="AW26">
-        <v>0</v>
-      </c>
-      <c r="AX26">
-        <v>0</v>
-      </c>
-      <c r="AY26">
-        <v>0</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>1.73</v>
-      </c>
-      <c r="BC26">
-        <v>2.25</v>
-      </c>
-      <c r="BD26" s="3">
         <v>45826.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-06-18.xlsx
+++ b/jogos_2025-06-18.xlsx
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
         <v>4.2</v>
       </c>
       <c r="N6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X6" t="n">
         <v>4.2</v>
       </c>
-      <c r="O6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X6" t="n">
-        <v>6.5</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.52</v>
+        <v>2.17</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['61', '90+3']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['45+2', '69', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.1</v>
+        <v>1.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.49</v>
+        <v>3.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45826.45833333334</v>
@@ -1288,109 +1288,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>1.55</v>
       </c>
       <c r="M7" t="n">
         <v>4.2</v>
       </c>
       <c r="N7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.4</v>
       </c>
-      <c r="O7" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['61', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['45+2', '69', '90']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH7" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['79']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AI7" t="n">
-        <v>3.2</v>
+        <v>1.49</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.42</v>
+        <v>2.7</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45826.45833333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.02</v>
+        <v>5.9</v>
       </c>
       <c r="M8" t="n">
-        <v>21.03</v>
+        <v>4.45</v>
       </c>
       <c r="N8" t="n">
-        <v>51</v>
+        <v>1.31</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>5.91</v>
       </c>
       <c r="P8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['14']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['3', '70']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI8" t="n">
         <v>4.75</v>
       </c>
-      <c r="Q8" t="n">
-        <v>17</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['25', '21', '88', '84']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45826.5</v>
@@ -1546,23 +1546,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="M9" t="n">
-        <v>3.74</v>
+        <v>21.03</v>
       </c>
       <c r="N9" t="n">
-        <v>1.98</v>
+        <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>17</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.37</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.48</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>4.15</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.66</v>
+        <v>1.13</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.92</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.42</v>
+        <v>2.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>['25', '21', '88', '84']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['88', '48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.68</v>
+        <v>1.02</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.6</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45826.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1693,7 +1693,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
-        <v>4.45</v>
+        <v>3.74</v>
       </c>
       <c r="N10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.31</v>
       </c>
-      <c r="O10" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.23</v>
-      </c>
       <c r="S10" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="U10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['88', '48']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.55</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X10" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['14']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['3', '70']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.2</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45826.5</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1948,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.31</v>
+        <v>2.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="X12" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['20', '18', '59']</t>
+          <t>['54', '88', '90+2']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AI12" t="n">
         <v>1.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45826.58333333334</v>
@@ -2062,109 +2062,109 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3</v>
       </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M13" t="n">
-        <v>4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.43</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T13" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="U13" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V13" t="n">
         <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>6.11</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['65', '78', '89']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45826.58333333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>6.93</v>
       </c>
       <c r="O14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z14" t="n">
         <v>2.45</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="AA14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['28']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AI14" t="n">
         <v>1.29</v>
       </c>
-      <c r="X14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['54', '88', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['51']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45826.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,109 +2320,109 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S15" t="n">
         <v>4</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="T15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['30', '52', '57', '83']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45826.58333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,22 +2578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>6.5</v>
+        <v>2.92</v>
       </c>
       <c r="O17" t="n">
-        <v>1.77</v>
+        <v>2.67</v>
       </c>
       <c r="P17" t="n">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.74</v>
+        <v>3.5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.16</v>
       </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['20', '18', '59']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI17" t="n">
         <v>1.73</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45826.58333333334</v>
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.4</v>
+        <v>3.56</v>
       </c>
       <c r="M18" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>6.93</v>
+        <v>1.96</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.59</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.5</v>
+        <v>2.43</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="X18" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['1']</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>['30', '52', '57', '83']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.88</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.29</v>
+        <v>2.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45826.58333333334</v>
@@ -2836,23 +2836,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
         <v>1</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.38</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.85</v>
+        <v>2.11</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4.43</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
         <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>6.11</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.43</v>
+        <v>2.35</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['65', '78', '89']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45826.58333333334</v>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>1.22</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>3.05</v>
+        <v>10.88</v>
       </c>
       <c r="O20" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="P20" t="n">
-        <v>2.23</v>
+        <v>3.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="T20" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>3.84</v>
+        <v>6.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.08</v>
+        <v>2.63</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['58', '68', '85']</t>
+          <t>['43', '35']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['39', '64']</t>
+          <t>['29', '78']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.67</v>
+        <v>3.9</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45826.58333333334</v>
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
         <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.22</v>
       </c>
-      <c r="M21" t="n">
-        <v>6</v>
-      </c>
-      <c r="N21" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="X21" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.57</v>
       </c>
-      <c r="P21" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X21" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['43', '35']</t>
+          <t>['58', '68', '85']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['29', '78']</t>
+          <t>['39', '64']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.9</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.17</v>
+        <v>2.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45826.58333333334</v>
@@ -3235,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -3245,65 +3245,65 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.02</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3312,14 +3312,14 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N27" t="n">
-        <v>6</v>
+        <v>2.38</v>
       </c>
       <c r="O27" t="n">
-        <v>2.15</v>
+        <v>3.38</v>
       </c>
       <c r="P27" t="n">
         <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.25</v>
+        <v>2.95</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="U27" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
         <v>1.28</v>
       </c>
-      <c r="X27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['29', '45+2', '88']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH27" t="n">
-        <v>2.25</v>
+        <v>1.38</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45826.875</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Birmingham Legion</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
         <v>1</v>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>2.38</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>3.38</v>
+        <v>2.15</v>
       </c>
       <c r="P28" t="n">
         <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.95</v>
+        <v>5.25</v>
       </c>
       <c r="R28" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T28" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="U28" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
-        <v>3.06</v>
+        <v>3.55</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['29', '45+2', '88']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.38</v>
+        <v>2.25</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45826.875</v>
